--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Email</t>
   </si>
@@ -98,28 +98,10 @@
     <t>EldonTrantow@yopmail.com</t>
   </si>
   <si>
-    <t>JeramyWest@yopmail.com</t>
-  </si>
-  <si>
-    <t>AlexKoch@yopmail.com</t>
-  </si>
-  <si>
-    <t>KarrenBarton@yopmail.com</t>
-  </si>
-  <si>
-    <t>EddieArmstrong@yopmail.com</t>
-  </si>
-  <si>
-    <t>AgripinaBartoletti@yopmail.com</t>
-  </si>
-  <si>
-    <t>ClaraKassulke@yopmail.com</t>
-  </si>
-  <si>
-    <t>IluminadaParisianV@yopmail.com</t>
-  </si>
-  <si>
-    <t>ShanaSawayn@yopmail.com</t>
+    <t>VeolaConsidine@yopmail.com</t>
+  </si>
+  <si>
+    <t>YvoneBerge@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1261,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1407,36 +1389,6 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="s" s="0">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="0">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="0">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s" s="0">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s" s="0">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Email</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>EldonTrantow@yopmail.com</t>
+  </si>
+  <si>
+    <t>MichelNikolaus@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1373,6 +1376,11 @@
         <v>22</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Email</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>EldonTrantow@yopmail.com</t>
+  </si>
+  <si>
+    <t>MsDeeHettinger@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1258,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1373,6 +1376,11 @@
         <v>22</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
   <si>
     <t>Email</t>
   </si>
@@ -99,6 +99,21 @@
   </si>
   <si>
     <t>MsDeeHettinger@yopmail.com</t>
+  </si>
+  <si>
+    <t>MrWinfordAbernathy@yopmail.com</t>
+  </si>
+  <si>
+    <t>TonieMarks@yopmail.com</t>
+  </si>
+  <si>
+    <t>MichaelShanahan@yopmail.com</t>
+  </si>
+  <si>
+    <t>SuziBlock@yopmail.com</t>
+  </si>
+  <si>
+    <t>LenKonopelski@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1258,7 +1273,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1381,6 +1396,31 @@
         <v>23</v>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>Email</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>LenKonopelski@yopmail.com</t>
+  </si>
+  <si>
+    <t>GaleHuel@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1273,7 +1276,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1421,6 +1424,11 @@
         <v>28</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>Email</t>
   </si>
@@ -156,6 +156,15 @@
   </si>
   <si>
     <t>LawrenceAltenwerth@yopmail.com</t>
+  </si>
+  <si>
+    <t>SamellaDaniel@yopmail.com</t>
+  </si>
+  <si>
+    <t>CurtSkiles@yopmail.com</t>
+  </si>
+  <si>
+    <t>GeneReilly@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1315,7 +1324,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1533,6 +1542,21 @@
         <v>42</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -50,6 +50,24 @@
   </si>
   <si>
     <t>rohank90031@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90032@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90033@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90034@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90036@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90035@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90037@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1536,6 +1554,36 @@
         <v>11</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -68,6 +68,42 @@
   </si>
   <si>
     <t>rohank90037@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90040@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90039@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90038@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90043@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90041@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90042@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90046@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90044@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90045@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90048@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90047@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90049@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1477,7 +1513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1584,6 +1620,66 @@
         <v>17</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -104,6 +104,21 @@
   </si>
   <si>
     <t>rohank90049@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90051@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90052@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90055@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90053@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90054@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1513,7 +1528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1680,6 +1695,31 @@
         <v>29</v>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -119,6 +119,24 @@
   </si>
   <si>
     <t>rohank90054@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90057@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90058@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90056@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90059@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90060@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90061@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1528,7 +1546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A37"/>
+  <dimension ref="A1:A43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1720,6 +1738,36 @@
         <v>34</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -155,6 +155,24 @@
   </si>
   <si>
     <t>rohank90065@maildrop.cc</t>
+  </si>
+  <si>
+    <t>HassieBrown@yopmail.com</t>
+  </si>
+  <si>
+    <t>rohank90069@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90068@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90071@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90072@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90073@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1393,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A25"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1551,6 +1569,11 @@
         <is>
           <t>YvoneBerge@yopmail.com</t>
         </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1564,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1816,6 +1839,31 @@
         <v>46</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>52</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -173,6 +173,24 @@
   </si>
   <si>
     <t>rohank90073@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90076@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90075@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90074@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90078@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90079@maildrop.cc</t>
+  </si>
+  <si>
+    <t>rohank90077@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1587,7 +1605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A54"/>
+  <dimension ref="A1:A60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1864,6 +1882,36 @@
         <v>52</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>58</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Email</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>AnnisDenesik@yopmail.com</t>
+  </si>
+  <si>
+    <t>DudleyMitchell@yopmail.com</t>
+  </si>
+  <si>
+    <t>AltheaJones@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1333,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A49"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1565,6 +1571,16 @@
         <v>46</v>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Email</t>
   </si>
@@ -156,6 +156,33 @@
   </si>
   <si>
     <t>LawrenceAltenwerth@yopmail.com</t>
+  </si>
+  <si>
+    <t>CraigMayerJr@yopmail.com</t>
+  </si>
+  <si>
+    <t>NoeTorphy@yopmail.com</t>
+  </si>
+  <si>
+    <t>ElsaThompson@yopmail.com</t>
+  </si>
+  <si>
+    <t>MadelineQuitzon@yopmail.com</t>
+  </si>
+  <si>
+    <t>LenoreHansen@yopmail.com</t>
+  </si>
+  <si>
+    <t>MrsKenethChristiansen@yopmail.com</t>
+  </si>
+  <si>
+    <t>CathieKuhlman@yopmail.com</t>
+  </si>
+  <si>
+    <t>MoisesLehner@yopmail.com</t>
+  </si>
+  <si>
+    <t>RefugioFeeney@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1315,7 +1342,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A43"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1533,6 +1560,51 @@
         <v>42</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>51</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Email</t>
   </si>
@@ -174,6 +174,9 @@
   </si>
   <si>
     <t>AltheaJones@yopmail.com</t>
+  </si>
+  <si>
+    <t>VincentDAmorePhD@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1333,7 +1336,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:A49"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -1581,6 +1584,11 @@
         <v>48</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -311,6 +311,42 @@
   </si>
   <si>
     <t>rohank90120@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000002@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000003@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000001@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000006@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000004@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000005@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000007@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000008@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000009@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000012@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000010@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000011@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1725,7 +1761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A100"/>
+  <dimension ref="A1:A112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2232,6 +2268,66 @@
         <v>98</v>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>110</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -347,6 +347,24 @@
   </si>
   <si>
     <t>yc000011@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000014@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000015@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000013@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000018@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000016@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000017@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1761,7 +1779,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A112"/>
+  <dimension ref="A1:A118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +2346,36 @@
         <v>110</v>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -365,6 +365,24 @@
   </si>
   <si>
     <t>yc000017@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000021@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000019@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000020@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000024@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000023@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000022@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1779,7 +1797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A118"/>
+  <dimension ref="A1:A124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2376,6 +2394,36 @@
         <v>116</v>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s" s="0">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -383,6 +383,42 @@
   </si>
   <si>
     <t>yc000022@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000026@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000025@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000027@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000028@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000030@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000029@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000031@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000033@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000032@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000035@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000034@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yc000036@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1797,7 +1833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A124"/>
+  <dimension ref="A1:A136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2424,6 +2460,66 @@
         <v>122</v>
       </c>
     </row>
+    <row r="125">
+      <c r="A125" t="s" s="0">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="0">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="0">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="0">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="0">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="0">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s" s="0">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s" s="0">
+        <v>134</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -419,6 +419,24 @@
   </si>
   <si>
     <t>yc000036@maildrop.cc</t>
+  </si>
+  <si>
+    <t>ycc00002@maildrop.cc</t>
+  </si>
+  <si>
+    <t>ycc00001@maildrop.cc</t>
+  </si>
+  <si>
+    <t>ycc00004@maildrop.cc</t>
+  </si>
+  <si>
+    <t>ycc00003@maildrop.cc</t>
+  </si>
+  <si>
+    <t>ycc00005@maildrop.cc</t>
+  </si>
+  <si>
+    <t>ycc00006@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1833,7 +1851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A136"/>
+  <dimension ref="A1:A142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2520,6 +2538,36 @@
         <v>134</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="s" s="0">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s" s="0">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s" s="0">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s" s="0">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s" s="0">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s" s="0">
+        <v>140</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -437,6 +437,24 @@
   </si>
   <si>
     <t>ycc00006@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco41921@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco41920@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco41922@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco41923@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco41925@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco41924@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1851,7 +1869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A142"/>
+  <dimension ref="A1:A148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,6 +2586,36 @@
         <v>140</v>
       </c>
     </row>
+    <row r="143">
+      <c r="A143" t="s" s="0">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s" s="0">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s" s="0">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s" s="0">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="0">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s" s="0">
+        <v>146</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
   <si>
     <t>rohank90020@maildrop.cc</t>
   </si>
@@ -455,6 +455,45 @@
   </si>
   <si>
     <t>yco41924@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco43185@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco43184@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco43186@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco43187@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco43188@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco43189@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco44162@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco44161@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco44163@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco44165@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco44166@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco44167@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco44168@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1869,7 +1908,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A148"/>
+  <dimension ref="A1:A161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2616,6 +2655,71 @@
         <v>146</v>
       </c>
     </row>
+    <row r="149">
+      <c r="A149" t="s" s="0">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s" s="0">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s" s="0">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s" s="0">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s" s="0">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s" s="0">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s" s="0">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s" s="0">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s" s="0">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s" s="0">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s" s="0">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s" s="0">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s" s="0">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="32">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -89,6 +89,27 @@
   </si>
   <si>
     <t>Prerana Colony Apex Youth Club</t>
+  </si>
+  <si>
+    <t>yco2606241729m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606241729m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606241730m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606241730m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606241733m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606241733m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Sahyog Vihar Nova Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1515,7 +1536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1733,6 +1754,72 @@
         <v>8</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="C25" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="47">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -131,6 +131,30 @@
   </si>
   <si>
     <t>Nai Disha Enclave Beta Youth Club</t>
+  </si>
+  <si>
+    <t>FredKuhicPhD@yopmail.com</t>
+  </si>
+  <si>
+    <t>yco2606271149m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271149m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271151m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271151m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271152m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271152m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Umang Nagar Nova Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1544,6 +1568,11 @@
     <row r="28">
       <c r="A28" t="s" s="0">
         <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1557,7 +1586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,6 +1936,72 @@
         <v>8</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="54">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -155,6 +155,27 @@
   </si>
   <si>
     <t>Umang Nagar Nova Youth Club</t>
+  </si>
+  <si>
+    <t>ChristeenJacobson@yopmail.com</t>
+  </si>
+  <si>
+    <t>yco2606271338m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271338m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271340m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271340m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271343m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271343m6@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A29"/>
+  <dimension ref="A1:A30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1573,6 +1594,11 @@
     <row r="29">
       <c r="A29" t="s" s="0">
         <v>39</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1586,7 +1612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C37"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2002,6 +2028,72 @@
         <v>8</v>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="62">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -176,6 +176,30 @@
   </si>
   <si>
     <t>yco2606271343m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>NatashaWisozkJr@yopmail.com</t>
+  </si>
+  <si>
+    <t>yco2606271421m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271421m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271422m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271422m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271423m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271423m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Yuva Shakti Puram Core Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1396,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A30"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1599,6 +1623,11 @@
     <row r="30">
       <c r="A30" t="s" s="0">
         <v>47</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1612,7 +1641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2094,6 +2123,72 @@
         <v>1</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="62">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -131,6 +131,75 @@
   </si>
   <si>
     <t>Nai Disha Enclave Beta Youth Club</t>
+  </si>
+  <si>
+    <t>FredKuhicPhD@yopmail.com</t>
+  </si>
+  <si>
+    <t>yco2606271149m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271149m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271151m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271151m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271152m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271152m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Umang Nagar Nova Youth Club</t>
+  </si>
+  <si>
+    <t>ChristeenJacobson@yopmail.com</t>
+  </si>
+  <si>
+    <t>yco2606271338m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271338m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271340m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271340m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271343m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271343m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>NatashaWisozkJr@yopmail.com</t>
+  </si>
+  <si>
+    <t>yco2606271421m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271421m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271422m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271422m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271423m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606271423m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Yuva Shakti Puram Core Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1351,7 +1420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1544,6 +1613,21 @@
     <row r="28">
       <c r="A28" t="s" s="0">
         <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1557,7 +1641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,6 +1991,204 @@
         <v>8</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="53">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -131,6 +131,48 @@
   </si>
   <si>
     <t>Nai Disha Enclave Beta Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607032218m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032222m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032222m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032223m7@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032223m8@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032254m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032257m8@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032321m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032321m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032322m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032322m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032324m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032324m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Pragati Block Alpha Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1907,6 +1949,149 @@
         <v>8</v>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B33" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="B34" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B36" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="B39" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C39" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="0">
+        <v>47</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C40" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="B41" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C41" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="B42" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C42" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="0">
+        <v>50</v>
+      </c>
+      <c r="B43" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C43" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="B44" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C44" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="60">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -173,6 +173,27 @@
   </si>
   <si>
     <t>Pragati Block Alpha Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607032344m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032344m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032346m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032346m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032348m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607032348m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Navjyoti Ward Sigma Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1599,7 +1620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2092,6 +2113,72 @@
         <v>8</v>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" t="s" s="0">
+        <v>53</v>
+      </c>
+      <c r="B45" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C45" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C46" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="B47" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C47" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="0">
+        <v>56</v>
+      </c>
+      <c r="B48" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C48" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="0">
+        <v>57</v>
+      </c>
+      <c r="B49" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C49" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="67">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -194,6 +194,27 @@
   </si>
   <si>
     <t>Navjyoti Ward Sigma Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607041218m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041218m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041220m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041220m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041223m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041223m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Umang Sector Beta Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1620,7 +1641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C50"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2179,6 +2200,72 @@
         <v>8</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>60</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>61</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>62</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="83">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -215,6 +215,54 @@
   </si>
   <si>
     <t>Umang Sector Beta Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607041304m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041304m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041306m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041306m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041307m8@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041307m7@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Udaan Mohalla Delta Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607041440m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041441m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041441m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041443m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041443m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041444m8@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041444m7@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Not Used</t>
+  </si>
+  <si>
+    <t>Jagriti Sector Nova Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1641,7 +1689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2266,6 +2314,149 @@
         <v>8</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B64" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C64" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B65" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C65" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B66" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C66" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C67" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="B68" t="s" s="0">
+        <v>82</v>
+      </c>
+      <c r="C68" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="0">
+        <v>80</v>
+      </c>
+      <c r="B69" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="128">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -263,6 +263,141 @@
   </si>
   <si>
     <t>Jagriti Sector Nova Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607041757m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041757m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041758m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041758m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041759m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041759m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041836m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041836m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041837m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041837m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041839m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041839m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041915m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041915m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041918m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041918m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041919m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041919m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041928m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041928m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041929m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041929m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041930m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607041930m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607042023m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607042023m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607042024m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607042024m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607042025m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607042025m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Vikas Basti Elite Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607050018m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607050018m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607050020m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607050020m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607050022m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607050022m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Sankalp Enclave Sigma Youth Club</t>
+  </si>
+  <si>
+    <t>yco2607050046m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607050046m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607050048m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607050048m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607050049m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607050049m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Sahyog Mohalla Elite Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1689,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C69"/>
+  <dimension ref="A1:C111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2457,6 +2592,468 @@
         <v>81</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" t="s" s="0">
+        <v>83</v>
+      </c>
+      <c r="B70" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="0">
+        <v>84</v>
+      </c>
+      <c r="B71" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="B72" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="B73" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="B74" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="0">
+        <v>88</v>
+      </c>
+      <c r="B75" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="0">
+        <v>89</v>
+      </c>
+      <c r="B76" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="0">
+        <v>90</v>
+      </c>
+      <c r="B77" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="0">
+        <v>91</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="0">
+        <v>92</v>
+      </c>
+      <c r="B79" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="0">
+        <v>93</v>
+      </c>
+      <c r="B80" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="0">
+        <v>94</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="0">
+        <v>95</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="0">
+        <v>96</v>
+      </c>
+      <c r="B83" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B84" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="B85" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="0">
+        <v>99</v>
+      </c>
+      <c r="B86" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="B87" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="B88" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="0">
+        <v>103</v>
+      </c>
+      <c r="B90" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="0">
+        <v>104</v>
+      </c>
+      <c r="B91" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="0">
+        <v>105</v>
+      </c>
+      <c r="B92" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C93" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B94" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C94" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="B95" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C95" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B96" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C96" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="B97" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C97" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="B98" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C98" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B99" t="s" s="0">
+        <v>113</v>
+      </c>
+      <c r="C99" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="B100" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C100" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="B101" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C101" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B102" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C102" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="B103" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C103" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s" s="0">
+        <v>118</v>
+      </c>
+      <c r="B104" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C104" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s" s="0">
+        <v>119</v>
+      </c>
+      <c r="B105" t="s" s="0">
+        <v>120</v>
+      </c>
+      <c r="C105" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s" s="0">
+        <v>121</v>
+      </c>
+      <c r="B106" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C106" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="0">
+        <v>122</v>
+      </c>
+      <c r="B107" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C107" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="0">
+        <v>123</v>
+      </c>
+      <c r="B108" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C108" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="0">
+        <v>124</v>
+      </c>
+      <c r="B109" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C109" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s" s="0">
+        <v>125</v>
+      </c>
+      <c r="B110" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C110" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="0">
+        <v>126</v>
+      </c>
+      <c r="B111" t="s" s="0">
+        <v>127</v>
+      </c>
+      <c r="C111" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="83">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -200,6 +200,69 @@
   </si>
   <si>
     <t>Yuva Shakti Puram Core Youth Club</t>
+  </si>
+  <si>
+    <t>MrsNadiaZboncak@yopmail.com</t>
+  </si>
+  <si>
+    <t>yco2606292151m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606292151m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606292153m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606292153m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606292154m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606292154m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>EliDaniel@yopmail.com</t>
+  </si>
+  <si>
+    <t>yco2606292202m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606292202m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606301012m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606301012m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606301014m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606301014m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606301016m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2606301016m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Navjyoti Puram Nova Youth Club</t>
+  </si>
+  <si>
+    <t>KennyFeeneyDDS@yopmail.com</t>
+  </si>
+  <si>
+    <t>TwandaJenkins@yopmail.com</t>
+  </si>
+  <si>
+    <t>LinwoodWill@yopmail.com</t>
+  </si>
+  <si>
+    <t>AugustWilliamson@yopmail.com</t>
   </si>
 </sst>
 </file>
@@ -1420,7 +1483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A31"/>
+  <dimension ref="A1:A37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1628,6 +1691,36 @@
     <row r="31">
       <c r="A31" t="s" s="0">
         <v>54</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="0">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="0">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="0">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -1641,7 +1734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2189,6 +2282,160 @@
         <v>8</v>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="B50" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s" s="0">
+        <v>64</v>
+      </c>
+      <c r="B51" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="0">
+        <v>65</v>
+      </c>
+      <c r="B52" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s" s="0">
+        <v>66</v>
+      </c>
+      <c r="B53" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s" s="0">
+        <v>67</v>
+      </c>
+      <c r="B54" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s" s="0">
+        <v>68</v>
+      </c>
+      <c r="B55" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s" s="0">
+        <v>71</v>
+      </c>
+      <c r="B57" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s" s="0">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s" s="0">
+        <v>72</v>
+      </c>
+      <c r="B58" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C58" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="0">
+        <v>73</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C59" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B60" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C60" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="B61" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C61" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="0">
+        <v>76</v>
+      </c>
+      <c r="B62" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C62" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B63" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C63" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="132">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -398,6 +398,18 @@
   </si>
   <si>
     <t>Sahyog Mohalla Elite Youth Club</t>
+  </si>
+  <si>
+    <t>BrittHintz@maildrop.cc</t>
+  </si>
+  <si>
+    <t>MissGulgowski@maildrop.cc</t>
+  </si>
+  <si>
+    <t>SonBrekke@maildrop.cc</t>
+  </si>
+  <si>
+    <t>CharoletteGusikowski@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -1618,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A28"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1811,6 +1823,26 @@
     <row r="28">
       <c r="A28" t="s" s="0">
         <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="148">
   <si>
     <t>yco71304@maildrop.cc</t>
   </si>
@@ -410,6 +410,54 @@
   </si>
   <si>
     <t>CharoletteGusikowski@maildrop.cc</t>
+  </si>
+  <si>
+    <t>HarryHeller@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070926m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070926m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070928m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070928m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070929m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070929m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Umang Mohalla Alpha Youth Club</t>
+  </si>
+  <si>
+    <t>MrJesusHeidenreich@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070938m1@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070938m2@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070940m3@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070940m4@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070941m5@maildrop.cc</t>
+  </si>
+  <si>
+    <t>yco2607070941m6@maildrop.cc</t>
+  </si>
+  <si>
+    <t>Sahyog Enclave Nova Youth Club</t>
   </si>
 </sst>
 </file>
@@ -1630,7 +1678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
@@ -1843,6 +1891,16 @@
     <row r="32">
       <c r="A32" t="s" s="0">
         <v>131</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="0">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="0">
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -1856,7 +1914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C111"/>
+  <dimension ref="A1:C123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3086,6 +3144,138 @@
         <v>8</v>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="s" s="0">
+        <v>133</v>
+      </c>
+      <c r="B112" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="C112" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s" s="0">
+        <v>134</v>
+      </c>
+      <c r="B113" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="C113" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="0">
+        <v>135</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="C114" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s" s="0">
+        <v>136</v>
+      </c>
+      <c r="B115" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="C115" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s" s="0">
+        <v>137</v>
+      </c>
+      <c r="B116" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="C116" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s" s="0">
+        <v>138</v>
+      </c>
+      <c r="B117" t="s" s="0">
+        <v>139</v>
+      </c>
+      <c r="C117" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s" s="0">
+        <v>141</v>
+      </c>
+      <c r="B118" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C118" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s" s="0">
+        <v>142</v>
+      </c>
+      <c r="B119" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C119" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s" s="0">
+        <v>143</v>
+      </c>
+      <c r="B120" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C120" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s" s="0">
+        <v>144</v>
+      </c>
+      <c r="B121" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C121" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s" s="0">
+        <v>145</v>
+      </c>
+      <c r="B122" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C122" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s" s="0">
+        <v>146</v>
+      </c>
+      <c r="B123" t="s" s="0">
+        <v>147</v>
+      </c>
+      <c r="C123" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/resources/Youth_prod.xlsx
+++ b/resources/Youth_prod.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="32">
   <si>
     <t>Email</t>
   </si>
@@ -106,6 +106,9 @@
   </si>
   <si>
     <t>Sankalp Vihar Elite Youth Club</t>
+  </si>
+  <si>
+    <t>ceolahomenick@maildrop.cc</t>
   </si>
 </sst>
 </file>
@@ -150,7 +153,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:A13"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -216,6 +219,11 @@
     <row r="13">
       <c r="A13" t="s" s="0">
         <v>23</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
